--- a/CLVSQLRESULTS.xlsx
+++ b/CLVSQLRESULTS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/320ab0493b2cf4b8/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/khristiannovoa/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBB3B0C1-D020-48C2-85E1-3E3CEE769B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{90C1BBBE-262A-0143-8B98-074E2E5C95CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22875" windowHeight="14356" xr2:uid="{8E248096-7E8A-4049-B0FA-FC279353E4B1}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="22880" windowHeight="14360" xr2:uid="{8E248096-7E8A-4049-B0FA-FC279353E4B1}"/>
   </bookViews>
   <sheets>
     <sheet name="SQL Code" sheetId="1" r:id="rId1"/>
@@ -6226,305 +6226,305 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E63D351C-00AD-4C7D-9FA3-E7999771A70C}">
   <dimension ref="A1:A60"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="106.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>52</v>
       </c>
@@ -6537,14 +6537,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1ADA02C-2F2E-4754-876D-79FE0D7851CF}">
   <dimension ref="A1:O14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.9296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>53</v>
       </c>
@@ -6591,7 +6591,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>44136</v>
       </c>
@@ -6638,7 +6638,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>44143</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>44150</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>44157</v>
       </c>
@@ -6779,7 +6779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>44164</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>44171</v>
       </c>
@@ -6873,7 +6873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>44178</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>44185</v>
       </c>
@@ -6967,7 +6967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>44192</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>44199</v>
       </c>
@@ -7061,7 +7061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>44206</v>
       </c>
@@ -7108,7 +7108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>44213</v>
       </c>
@@ -7155,7 +7155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>44220</v>
       </c>
